--- a/Тест2/210.xlsx
+++ b/Тест2/210.xlsx
@@ -252,22 +252,22 @@
     <t xml:space="preserve">Immun bosqich leptospiremiyadan keyin nimani ko'rsatadi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Qo'zg'atuvchi sporalanishini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antitelolar ishlab chiqarilishi boshlanishini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaksina ta'sirining boshlanishini</t>
+    <t xml:space="preserve">Qo'zg'atuvchi sporalanganini ko'rsatadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antitelolar ishlab chiqarila boshlanishini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaksina ta'siri boshlanganini ko'rsatadi</t>
   </si>
   <si>
     <t xml:space="preserve">Qondagi qo'zg'atuvchi soni ortishini</t>
   </si>
   <si>
-    <t xml:space="preserve">Kasallikning butunlay tugashini</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To'g'ri javob: Antitelolar ishlab chiqarilishi boshlanishini. Leptospiremiya bosqichidan keyin immun tizim antitelolar ishlab chiqara boshlaydi. Manba: Mavzu materiali (210.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
+    <t xml:space="preserve">Kasallik butunlay tugaganini ko'rsatadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To'g'ri javob: Antitelolar ishlab chiqarila boshlanishini. Leptospiremiya bosqichidan keyin immun tizim antitelolar ishlab chiqara boshlaydi. Manba: Mavzu materiali (210.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
   </si>
 </sst>
 </file>
